--- a/partner_results/chmo/ClassMissingGermanLabel_chmo.xlsx
+++ b/partner_results/chmo/ClassMissingGermanLabel_chmo.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>laser-induced breakdown spectroscopy [chmo]</t>
+          <t>concentration output [chmo]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>measurement metadata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A type of atomic emission spectrometry where a high energy laser pulse is used to generate a plasma which acts as the excitation source.</t>
+          <t>Experimental method output expressing the contribution of one constituent to the composition of a mixture. (chmo defined)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>concentration output [chmo]</t>
+          <t>laser-induced breakdown spectroscopy [chmo]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>measurement metadata</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Experimental method output expressing the contribution of one constituent to the composition of a mixture. (chmo defined)</t>
+          <t>A type of atomic emission spectrometry where a high energy laser pulse is used to generate a plasma which acts as the excitation source.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
